--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487011_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487011_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.1702</v>
+        <v>5.2645</v>
       </c>
       <c r="E2" t="n">
-        <v>3.7012</v>
+        <v>2.5661</v>
       </c>
       <c r="F2" t="n">
-        <v>3.4691</v>
+        <v>2.6984</v>
       </c>
       <c r="G2" t="n">
         <v>2.1901</v>
@@ -610,13 +610,13 @@
         <v>1.8481</v>
       </c>
       <c r="S2" t="n">
-        <v>3.7829</v>
+        <v>1.8772</v>
       </c>
       <c r="T2" t="n">
-        <v>2.0803</v>
+        <v>0.9452</v>
       </c>
       <c r="U2" t="n">
-        <v>1.7027</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="V2" t="n">
         <v>-0.2402</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. ENABULELE OGUNSUYI</t>
+          <t>A. RIVAS PALMER</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.8512</v>
+        <v>3.8743</v>
       </c>
       <c r="E3" t="n">
-        <v>4.5131</v>
+        <v>1.0962</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3381</v>
+        <v>2.7782</v>
       </c>
       <c r="G3" t="n">
-        <v>3.0621</v>
+        <v>3.458</v>
       </c>
       <c r="H3" t="n">
-        <v>3.1173</v>
+        <v>0.2432</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.0552</v>
+        <v>3.2148</v>
       </c>
       <c r="J3" t="n">
-        <v>3.9558</v>
+        <v>3.3202</v>
       </c>
       <c r="K3" t="n">
-        <v>3.6401</v>
+        <v>0.5713</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3157</v>
+        <v>2.7488</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.8937</v>
+        <v>0.1378</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.5228</v>
+        <v>-0.3281</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.3709</v>
+        <v>0.4659</v>
       </c>
       <c r="P3" t="n">
-        <v>0.4107</v>
+        <v>-0.616</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.2321</v>
+        <v>-2.4641</v>
       </c>
       <c r="R3" t="n">
-        <v>1.6427</v>
+        <v>1.8481</v>
       </c>
       <c r="S3" t="n">
-        <v>1.7275</v>
+        <v>0.3342</v>
       </c>
       <c r="T3" t="n">
-        <v>2.1384</v>
+        <v>0.2401</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4109</v>
+        <v>0.0941</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.3491</v>
+        <v>0.6982</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.3491</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>0.6982</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. RIVAS PALMER</t>
+          <t>M. ENABULELE OGUNSUYI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.1315</v>
+        <v>3.5548</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2051</v>
+        <v>3.2463</v>
       </c>
       <c r="F4" t="n">
-        <v>2.9264</v>
+        <v>0.3085</v>
       </c>
       <c r="G4" t="n">
-        <v>3.458</v>
+        <v>3.0621</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2432</v>
+        <v>3.1173</v>
       </c>
       <c r="I4" t="n">
-        <v>3.2148</v>
+        <v>-0.0552</v>
       </c>
       <c r="J4" t="n">
-        <v>3.3202</v>
+        <v>3.9558</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5713</v>
+        <v>3.6401</v>
       </c>
       <c r="L4" t="n">
-        <v>2.7488</v>
+        <v>0.3157</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1378</v>
+        <v>-0.8937</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.3281</v>
+        <v>-0.5228</v>
       </c>
       <c r="O4" t="n">
-        <v>0.4659</v>
+        <v>-0.3709</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.616</v>
+        <v>0.4107</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.4641</v>
+        <v>-1.2321</v>
       </c>
       <c r="R4" t="n">
-        <v>1.8481</v>
+        <v>1.6427</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.4087</v>
+        <v>0.431</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.651</v>
+        <v>0.8716</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2423</v>
+        <v>-0.4406</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6982</v>
+        <v>-0.3491</v>
       </c>
       <c r="W4" t="n">
+        <v>-0.3491</v>
+      </c>
+      <c r="X4" t="n">
         <v>0</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0.6982</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.818</v>
+        <v>3.1046</v>
       </c>
       <c r="E5" t="n">
-        <v>3.2096</v>
+        <v>3.4072</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3916</v>
+        <v>-0.3027</v>
       </c>
       <c r="G5" t="n">
         <v>2.8328</v>
@@ -844,13 +844,13 @@
         <v>1.2321</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2119</v>
+        <v>0.0746</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0464</v>
+        <v>0.244</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2583</v>
+        <v>-0.1694</v>
       </c>
       <c r="V5" t="n">
         <v>-0.8295</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>K. CLEMENT AIGBOGUN</t>
+          <t>A. MEANA PEREZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5593</v>
+        <v>1.4631</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.0688</v>
+        <v>1.0071</v>
       </c>
       <c r="F6" t="n">
-        <v>1.6282</v>
+        <v>0.456</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.4658</v>
+        <v>4.8471</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.9765</v>
+        <v>-1.7909</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.4893</v>
+        <v>6.6379</v>
       </c>
       <c r="J6" t="n">
-        <v>-2.1009</v>
+        <v>4.5407</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.2852</v>
+        <v>-1.3524</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.8158</v>
+        <v>5.8931</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.3649</v>
+        <v>0.3064</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.6913</v>
+        <v>-0.4385</v>
       </c>
       <c r="O6" t="n">
-        <v>0.3264</v>
+        <v>0.7449</v>
       </c>
       <c r="P6" t="n">
-        <v>0.616</v>
+        <v>-0.8214</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.4374</v>
+        <v>-3.6962</v>
       </c>
       <c r="R6" t="n">
-        <v>2.0534</v>
+        <v>2.8748</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2921</v>
+        <v>0.0349</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1122</v>
+        <v>0.1626</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1799</v>
+        <v>-0.1277</v>
       </c>
       <c r="V6" t="n">
-        <v>2.117</v>
+        <v>-2.5975</v>
       </c>
       <c r="W6" t="n">
-        <v>2.3573</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.2402</v>
+        <v>-2.5975</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S. GALLEGO MOGRO</t>
+          <t>K. CLEMENT AIGBOGUN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1767</v>
+        <v>1.228</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6267</v>
+        <v>-0.5187</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.45</v>
+        <v>1.7467</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.3323</v>
+        <v>-2.4658</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.2901</v>
+        <v>-0.9765</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.0421</v>
+        <v>-1.4893</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.7068</v>
+        <v>-2.1009</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.4302</v>
+        <v>-0.2852</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7234</v>
+        <v>-1.8158</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.6255</v>
+        <v>-0.3649</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.8599</v>
+        <v>-0.6913</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.7655999999999999</v>
+        <v>0.3264</v>
       </c>
       <c r="P7" t="n">
-        <v>1.8481</v>
+        <v>0.616</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.2053</v>
+        <v>-1.4374</v>
       </c>
       <c r="R7" t="n">
         <v>2.0534</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4207</v>
+        <v>0.9608</v>
       </c>
       <c r="T7" t="n">
-        <v>0.12</v>
+        <v>0.6624</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3007</v>
+        <v>0.2985</v>
       </c>
       <c r="V7" t="n">
-        <v>0.2402</v>
+        <v>2.117</v>
       </c>
       <c r="W7" t="n">
-        <v>1.4189</v>
+        <v>2.3573</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.1786</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. MEANA PEREZ</t>
+          <t>S. GALLEGO MOGRO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.08599999999999999</v>
+        <v>0.3604</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1862</v>
+        <v>0.9288999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1003</v>
+        <v>-0.5685</v>
       </c>
       <c r="G8" t="n">
-        <v>4.8471</v>
+        <v>-2.3323</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.7909</v>
+        <v>-2.2901</v>
       </c>
       <c r="I8" t="n">
-        <v>6.6379</v>
+        <v>-0.0421</v>
       </c>
       <c r="J8" t="n">
-        <v>4.5407</v>
+        <v>-0.7068</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.3524</v>
+        <v>-1.4302</v>
       </c>
       <c r="L8" t="n">
-        <v>5.8931</v>
+        <v>0.7234</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3064</v>
+        <v>-1.6255</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.4385</v>
+        <v>-0.8599</v>
       </c>
       <c r="O8" t="n">
-        <v>0.7449</v>
+        <v>-0.7655999999999999</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.8214</v>
+        <v>1.8481</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.6962</v>
+        <v>-0.2053</v>
       </c>
       <c r="R8" t="n">
-        <v>2.8748</v>
+        <v>2.0534</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.5142</v>
+        <v>0.6042999999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.0308</v>
+        <v>0.4222</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4834</v>
+        <v>0.1822</v>
       </c>
       <c r="V8" t="n">
-        <v>-2.5975</v>
+        <v>0.2402</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.4189</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.5975</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.2478</v>
+        <v>0.1961</v>
       </c>
       <c r="E9" t="n">
-        <v>1.4862</v>
+        <v>1.7226</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.734</v>
+        <v>-1.5265</v>
       </c>
       <c r="G9" t="n">
         <v>1.18</v>
@@ -1156,13 +1156,13 @@
         <v>0.8214</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0438</v>
+        <v>0.4</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2362</v>
+        <v>0.4726</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2801</v>
+        <v>-0.0726</v>
       </c>
       <c r="V9" t="n">
         <v>-1.1786</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.4371</v>
+        <v>0.1929</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.0456</v>
+        <v>0.4658</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.3914</v>
+        <v>-0.2729</v>
       </c>
       <c r="G10" t="n">
         <v>2.0879</v>
@@ -1234,13 +1234,13 @@
         <v>1.4374</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6687</v>
+        <v>-0.0387</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2558</v>
+        <v>0.2557</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.413</v>
+        <v>-0.2944</v>
       </c>
       <c r="V10" t="n">
         <v>-0.8295</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.9784</v>
+        <v>-0.9059</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.1846</v>
+        <v>-0.0528</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.7938</v>
+        <v>-0.8531</v>
       </c>
       <c r="G11" t="n">
         <v>0.387</v>
@@ -1312,13 +1312,13 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1867</v>
+        <v>-0.1143</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2635</v>
+        <v>-0.1317</v>
       </c>
       <c r="U11" t="n">
-        <v>0.07679999999999999</v>
+        <v>0.0175</v>
       </c>
       <c r="V11" t="n">
         <v>-1.1786</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.9457</v>
+        <v>-3.2564</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.31</v>
+        <v>-3.7986</v>
       </c>
       <c r="F12" t="n">
-        <v>0.3643</v>
+        <v>0.5422</v>
       </c>
       <c r="G12" t="n">
         <v>-0.7438</v>
@@ -1390,13 +1390,13 @@
         <v>1.2321</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3271</v>
+        <v>0.3622</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4457</v>
+        <v>0.0658</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1186</v>
+        <v>0.2964</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.3735</v>
+        <v>-4.8028</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.38</v>
+        <v>-4.8686</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0064</v>
+        <v>0.06569999999999999</v>
       </c>
       <c r="G13" t="n">
         <v>-5.2154</v>
@@ -1468,13 +1468,13 @@
         <v>1.4374</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.3901</v>
+        <v>-0.8194</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.8486</v>
+        <v>-0.3372</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.5415</v>
+        <v>-0.4823</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,19 +1501,19 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.638399999999999</v>
+        <v>10.2736</v>
       </c>
       <c r="E14" t="n">
-        <v>2.566700000000001</v>
+        <v>5.2015</v>
       </c>
       <c r="F14" t="n">
-        <v>5.072000000000001</v>
+        <v>5.072</v>
       </c>
       <c r="G14" t="n">
-        <v>9.287700000000001</v>
+        <v>9.287699999999997</v>
       </c>
       <c r="H14" t="n">
-        <v>-5.5639</v>
+        <v>-5.563899999999999</v>
       </c>
       <c r="I14" t="n">
         <v>14.8516</v>
@@ -1546,13 +1546,13 @@
         <v>18.4809</v>
       </c>
       <c r="S14" t="n">
-        <v>1.472000000000001</v>
+        <v>4.106799999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>1.2381</v>
+        <v>3.8733</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2338000000000001</v>
+        <v>0.2337</v>
       </c>
       <c r="V14" t="n">
         <v>-4.147600000000001</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.6226</v>
+        <v>4.578</v>
       </c>
       <c r="E15" t="n">
-        <v>4.642</v>
+        <v>5.0604</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.0194</v>
+        <v>-0.4824</v>
       </c>
       <c r="G15" t="n">
         <v>3.729</v>
@@ -1624,13 +1624,13 @@
         <v>2.4641</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.3815</v>
+        <v>-0.4261</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7014</v>
+        <v>-0.283</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.6801</v>
+        <v>-0.1431</v>
       </c>
       <c r="V15" t="n">
         <v>1.0698</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.4422</v>
+        <v>2.831</v>
       </c>
       <c r="E16" t="n">
         <v>0.796</v>
       </c>
       <c r="F16" t="n">
-        <v>1.6463</v>
+        <v>2.035</v>
       </c>
       <c r="G16" t="n">
         <v>2.3065</v>
@@ -1702,13 +1702,13 @@
         <v>2.0534</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4536</v>
+        <v>-0.0649</v>
       </c>
       <c r="T16" t="n">
         <v>-0.283</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1706</v>
+        <v>0.2181</v>
       </c>
       <c r="V16" t="n">
         <v>0.5893</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7067</v>
+        <v>1.2733</v>
       </c>
       <c r="E17" t="n">
         <v>0.0808</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6259</v>
+        <v>1.1925</v>
       </c>
       <c r="G17" t="n">
         <v>-1.1325</v>
@@ -1780,13 +1780,13 @@
         <v>2.8748</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.6412</v>
+        <v>-0.0746</v>
       </c>
       <c r="T17" t="n">
         <v>-0.2094</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4318</v>
+        <v>0.1348</v>
       </c>
       <c r="V17" t="n">
         <v>1.6591</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5516</v>
+        <v>0.9003</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9255</v>
+        <v>1.1347</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.3739</v>
+        <v>-0.2344</v>
       </c>
       <c r="G18" t="n">
         <v>-0.132</v>
@@ -1858,13 +1858,13 @@
         <v>1.0267</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4416</v>
+        <v>-0.0929</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1822</v>
+        <v>0.027</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2594</v>
+        <v>-0.12</v>
       </c>
       <c r="V18" t="n">
         <v>2.3573</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. SOLER CIRUJEDA</t>
+          <t>J. BITJAA KODY</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3352</v>
+        <v>-0.3409</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2474</v>
+        <v>-0.5446</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.5826</v>
+        <v>0.2038</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.5293</v>
+        <v>1.3734</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1333</v>
+        <v>2.6148</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.6626</v>
+        <v>-1.2415</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.9621</v>
+        <v>2.772</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.3173</v>
+        <v>2.6931</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.6449</v>
+        <v>0.0789</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.5672</v>
+        <v>-1.3987</v>
       </c>
       <c r="N19" t="n">
-        <v>0.4505</v>
+        <v>-0.07829999999999999</v>
       </c>
       <c r="O19" t="n">
-        <v>-2.0177</v>
+        <v>-1.3204</v>
       </c>
       <c r="P19" t="n">
-        <v>0.2053</v>
+        <v>-0.8214</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.2321</v>
+        <v>-3.2855</v>
       </c>
       <c r="R19" t="n">
-        <v>1.4374</v>
+        <v>2.4641</v>
       </c>
       <c r="S19" t="n">
-        <v>0.5699</v>
+        <v>0.2858</v>
       </c>
       <c r="T19" t="n">
-        <v>1.0227</v>
+        <v>-0.0312</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4527</v>
+        <v>0.317</v>
       </c>
       <c r="V19" t="n">
-        <v>1.4189</v>
+        <v>-1.1786</v>
       </c>
       <c r="W19" t="n">
-        <v>1.4189</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. BITJAA KODY</t>
+          <t>J. SOLER CIRUJEDA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.5169</v>
+        <v>-0.8635</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.6492</v>
+        <v>-0.5895</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1323</v>
+        <v>-0.274</v>
       </c>
       <c r="G20" t="n">
-        <v>1.3734</v>
+        <v>-2.5293</v>
       </c>
       <c r="H20" t="n">
-        <v>2.6148</v>
+        <v>0.1333</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.2415</v>
+        <v>-2.6626</v>
       </c>
       <c r="J20" t="n">
-        <v>2.772</v>
+        <v>-0.9621</v>
       </c>
       <c r="K20" t="n">
-        <v>2.6931</v>
+        <v>-0.3173</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0789</v>
+        <v>-0.6449</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.3987</v>
+        <v>-1.5672</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.07829999999999999</v>
+        <v>0.4505</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.3204</v>
+        <v>-2.0177</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.8214</v>
+        <v>0.2053</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.2855</v>
+        <v>-1.2321</v>
       </c>
       <c r="R20" t="n">
-        <v>2.4641</v>
+        <v>1.4374</v>
       </c>
       <c r="S20" t="n">
-        <v>0.1097</v>
+        <v>0.0417</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1358</v>
+        <v>0.1858</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2455</v>
+        <v>-0.1442</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.1786</v>
+        <v>1.4189</v>
       </c>
       <c r="W20" t="n">
+        <v>1.4189</v>
+      </c>
+      <c r="X20" t="n">
         <v>0</v>
-      </c>
-      <c r="X20" t="n">
-        <v>-1.1786</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.4938</v>
+        <v>-2.3735</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.1842</v>
+        <v>-0.975</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.3096</v>
+        <v>-1.3985</v>
       </c>
       <c r="G21" t="n">
         <v>-4.7681</v>
@@ -2092,13 +2092,13 @@
         <v>2.0534</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0747</v>
+        <v>0.0455</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1086</v>
+        <v>0.1006</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0338</v>
+        <v>-0.0551</v>
       </c>
       <c r="V21" t="n">
         <v>1.5277</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.6094</v>
+        <v>-2.6322</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.9071</v>
+        <v>-1.8025</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.7024</v>
+        <v>-0.8297</v>
       </c>
       <c r="G22" t="n">
         <v>-3.3848</v>
@@ -2170,13 +2170,13 @@
         <v>1.0267</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0111</v>
+        <v>-0.0339</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1899</v>
+        <v>-0.0853</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1787</v>
+        <v>0.0514</v>
       </c>
       <c r="V22" t="n">
         <v>-0.2402</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.4384</v>
+        <v>-2.9468</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.6846</v>
+        <v>-2.3708</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.7538</v>
+        <v>-0.5759</v>
       </c>
       <c r="G23" t="n">
         <v>-1.9095</v>
@@ -2248,13 +2248,13 @@
         <v>1.0267</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.3503</v>
+        <v>0.1414</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3216</v>
+        <v>-0.0078</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0286</v>
+        <v>0.1492</v>
       </c>
       <c r="V23" t="n">
         <v>-1.1786</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.568</v>
+        <v>-5.9724</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.3384</v>
+        <v>-5.8615</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.2295</v>
+        <v>-0.1109</v>
       </c>
       <c r="G24" t="n">
         <v>-2.8403</v>
@@ -2326,13 +2326,13 @@
         <v>1.0267</v>
       </c>
       <c r="S24" t="n">
-        <v>1.2025</v>
+        <v>0.7981</v>
       </c>
       <c r="T24" t="n">
-        <v>0.8754999999999999</v>
+        <v>0.3524</v>
       </c>
       <c r="U24" t="n">
-        <v>0.3271</v>
+        <v>0.4457</v>
       </c>
       <c r="V24" t="n">
         <v>-1.8768</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-7.638599999999999</v>
+        <v>-5.5467</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.0718</v>
+        <v>-5.072000000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.5667</v>
+        <v>-0.4745</v>
       </c>
       <c r="G25" t="n">
         <v>-9.287599999999998</v>
@@ -2404,13 +2404,13 @@
         <v>17.454</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.4719</v>
+        <v>0.6201000000000001</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.2337</v>
+        <v>-0.2339000000000001</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.2381</v>
+        <v>0.8538</v>
       </c>
       <c r="V25" t="n">
         <v>4.147899999999999</v>
